--- a/pruebas/canar_promediostotal.xlsx
+++ b/pruebas/canar_promediostotal.xlsx
@@ -563,76 +563,76 @@
         <v>88.09999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>70.80714285714285</v>
+        <v>70.807</v>
       </c>
       <c r="D2" t="n">
-        <v>71.16470588235293</v>
+        <v>71.16500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>71.8111111111111</v>
+        <v>71.81100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>71.38888888888889</v>
+        <v>71.389</v>
       </c>
       <c r="G2" t="n">
-        <v>70.94374999999999</v>
+        <v>70.944</v>
       </c>
       <c r="H2" t="n">
-        <v>70.86875000000001</v>
+        <v>70.869</v>
       </c>
       <c r="I2" t="n">
-        <v>70.80555555555556</v>
+        <v>70.806</v>
       </c>
       <c r="J2" t="n">
         <v>70.625</v>
       </c>
       <c r="K2" t="n">
-        <v>70.9388888888889</v>
+        <v>70.93899999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>70.62777777777778</v>
+        <v>70.628</v>
       </c>
       <c r="M2" t="n">
-        <v>70.96470588235294</v>
+        <v>70.965</v>
       </c>
       <c r="N2" t="n">
-        <v>70.7375</v>
+        <v>70.738</v>
       </c>
       <c r="O2" t="n">
-        <v>71.27058823529411</v>
+        <v>71.271</v>
       </c>
       <c r="P2" t="n">
-        <v>70.75555555555555</v>
+        <v>70.756</v>
       </c>
       <c r="Q2" t="n">
-        <v>70.8125</v>
+        <v>70.812</v>
       </c>
       <c r="R2" t="n">
         <v>70.2</v>
       </c>
       <c r="S2" t="n">
-        <v>70.41875</v>
+        <v>70.419</v>
       </c>
       <c r="T2" t="n">
         <v>70.84999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>70.55000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="V2" t="n">
-        <v>70.27058823529411</v>
+        <v>70.271</v>
       </c>
       <c r="W2" t="n">
         <v>70.75</v>
       </c>
       <c r="X2" t="n">
-        <v>70.21764705882353</v>
+        <v>70.218</v>
       </c>
       <c r="Y2" t="n">
         <v>70.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>70.4875</v>
+        <v>70.488</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>70.67777777777778</v>
+        <v>70.678</v>
       </c>
       <c r="AE2" t="n">
-        <v>70.77777777777777</v>
+        <v>70.77800000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>70.73529411764706</v>
+        <v>70.735</v>
       </c>
       <c r="AG2" t="n">
-        <v>71.10555555555555</v>
+        <v>71.10599999999999</v>
       </c>
       <c r="AH2" t="n">
         <v>70.788</v>
@@ -680,16 +680,16 @@
         <v>89.3</v>
       </c>
       <c r="C3" t="n">
-        <v>93.27857142857144</v>
+        <v>93.279</v>
       </c>
       <c r="D3" t="n">
-        <v>94.10588235294118</v>
+        <v>94.10599999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>93.96666666666667</v>
+        <v>93.967</v>
       </c>
       <c r="F3" t="n">
-        <v>93.48888888888888</v>
+        <v>93.489</v>
       </c>
       <c r="G3" t="n">
         <v>93.52500000000001</v>
@@ -698,55 +698,55 @@
         <v>93.55</v>
       </c>
       <c r="I3" t="n">
-        <v>92.95555555555556</v>
+        <v>92.956</v>
       </c>
       <c r="J3" t="n">
-        <v>93.3625</v>
+        <v>93.36199999999999</v>
       </c>
       <c r="K3" t="n">
         <v>93.75</v>
       </c>
       <c r="L3" t="n">
-        <v>93.52222222222223</v>
+        <v>93.52200000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>93.92941176470588</v>
+        <v>93.929</v>
       </c>
       <c r="N3" t="n">
-        <v>94.00624999999999</v>
+        <v>94.006</v>
       </c>
       <c r="O3" t="n">
-        <v>93.65882352941176</v>
+        <v>93.65900000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>93.38333333333334</v>
+        <v>93.383</v>
       </c>
       <c r="Q3" t="n">
-        <v>92.71875</v>
+        <v>92.71899999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>92.98235294117647</v>
+        <v>92.982</v>
       </c>
       <c r="S3" t="n">
-        <v>93.41875</v>
+        <v>93.419</v>
       </c>
       <c r="T3" t="n">
         <v>93.75</v>
       </c>
       <c r="U3" t="n">
-        <v>93.36111111111111</v>
+        <v>93.361</v>
       </c>
       <c r="V3" t="n">
-        <v>92.32352941176471</v>
+        <v>92.324</v>
       </c>
       <c r="W3" t="n">
-        <v>93.08888888888889</v>
+        <v>93.089</v>
       </c>
       <c r="X3" t="n">
-        <v>93.07058823529412</v>
+        <v>93.071</v>
       </c>
       <c r="Y3" t="n">
-        <v>92.84444444444445</v>
+        <v>92.84399999999999</v>
       </c>
       <c r="Z3" t="n">
         <v>93.27500000000001</v>
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>92.72222222222223</v>
+        <v>92.72199999999999</v>
       </c>
       <c r="AE3" t="n">
-        <v>92.86666666666666</v>
+        <v>92.867</v>
       </c>
       <c r="AF3" t="n">
-        <v>93.08235294117648</v>
+        <v>93.08199999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>93.13333333333334</v>
+        <v>93.133</v>
       </c>
       <c r="AH3" t="n">
         <v>93.32599999999999</v>
@@ -797,73 +797,73 @@
         <v>90.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>75.97857142857143</v>
+        <v>75.979</v>
       </c>
       <c r="D4" t="n">
-        <v>74.90588235294118</v>
+        <v>74.90600000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>78.87777777777778</v>
+        <v>78.878</v>
       </c>
       <c r="F4" t="n">
-        <v>75.25555555555555</v>
+        <v>75.256</v>
       </c>
       <c r="G4" t="n">
-        <v>74.39375</v>
+        <v>74.39400000000001</v>
       </c>
       <c r="H4" t="n">
         <v>74.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>73.67777777777778</v>
+        <v>73.678</v>
       </c>
       <c r="J4" t="n">
-        <v>74.56874999999999</v>
+        <v>74.569</v>
       </c>
       <c r="K4" t="n">
-        <v>74.68333333333334</v>
+        <v>74.68300000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>74.41111111111111</v>
+        <v>74.411</v>
       </c>
       <c r="M4" t="n">
-        <v>74.91764705882352</v>
+        <v>74.91800000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>74.75624999999999</v>
+        <v>74.756</v>
       </c>
       <c r="O4" t="n">
-        <v>74.81764705882354</v>
+        <v>74.818</v>
       </c>
       <c r="P4" t="n">
-        <v>73.83333333333333</v>
+        <v>73.833</v>
       </c>
       <c r="Q4" t="n">
-        <v>74.08125</v>
+        <v>74.081</v>
       </c>
       <c r="R4" t="n">
-        <v>72.85294117647059</v>
+        <v>72.85299999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>74.43125000000001</v>
+        <v>74.431</v>
       </c>
       <c r="T4" t="n">
-        <v>74.47777777777777</v>
+        <v>74.47799999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>74.27222222222223</v>
+        <v>74.27200000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>74.0764705882353</v>
+        <v>74.07599999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>73.82777777777778</v>
+        <v>73.828</v>
       </c>
       <c r="X4" t="n">
-        <v>74.38823529411764</v>
+        <v>74.38800000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>74.19999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="Z4" t="n">
         <v>73.325</v>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>74.46666666666667</v>
+        <v>74.467</v>
       </c>
       <c r="AE4" t="n">
-        <v>73.42222222222222</v>
+        <v>73.422</v>
       </c>
       <c r="AF4" t="n">
-        <v>72.95882352941176</v>
+        <v>72.959</v>
       </c>
       <c r="AG4" t="n">
-        <v>73.36111111111111</v>
+        <v>73.361</v>
       </c>
       <c r="AH4" t="n">
         <v>74.422</v>
@@ -914,76 +914,76 @@
         <v>90.90000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>96.92857142857143</v>
+        <v>96.929</v>
       </c>
       <c r="D5" t="n">
-        <v>97.09411764705882</v>
+        <v>97.09399999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>96.54444444444444</v>
+        <v>96.544</v>
       </c>
       <c r="F5" t="n">
-        <v>97.12222222222222</v>
+        <v>97.122</v>
       </c>
       <c r="G5" t="n">
-        <v>97.09375</v>
+        <v>97.09399999999999</v>
       </c>
       <c r="H5" t="n">
         <v>97.7</v>
       </c>
       <c r="I5" t="n">
-        <v>97.27777777777777</v>
+        <v>97.27800000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>97.01875</v>
+        <v>97.01900000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>97.08333333333333</v>
+        <v>97.083</v>
       </c>
       <c r="L5" t="n">
         <v>96.45</v>
       </c>
       <c r="M5" t="n">
-        <v>96.54705882352941</v>
+        <v>96.547</v>
       </c>
       <c r="N5" t="n">
         <v>96.675</v>
       </c>
       <c r="O5" t="n">
-        <v>97.85294117647059</v>
+        <v>97.85299999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>97.26111111111112</v>
+        <v>97.261</v>
       </c>
       <c r="Q5" t="n">
-        <v>97.51875</v>
+        <v>97.51900000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>96.82941176470588</v>
+        <v>96.82899999999999</v>
       </c>
       <c r="S5" t="n">
         <v>95.875</v>
       </c>
       <c r="T5" t="n">
-        <v>96.88888888888889</v>
+        <v>96.889</v>
       </c>
       <c r="U5" t="n">
-        <v>96.91111111111111</v>
+        <v>96.911</v>
       </c>
       <c r="V5" t="n">
-        <v>96.9470588235294</v>
+        <v>96.947</v>
       </c>
       <c r="W5" t="n">
-        <v>97.83888888888889</v>
+        <v>97.839</v>
       </c>
       <c r="X5" t="n">
         <v>96.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>96.29444444444444</v>
+        <v>96.294</v>
       </c>
       <c r="Z5" t="n">
-        <v>97.41249999999999</v>
+        <v>97.41200000000001</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1001,16 +1001,16 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>97.32222222222222</v>
+        <v>97.322</v>
       </c>
       <c r="AE5" t="n">
-        <v>96.86111111111111</v>
+        <v>96.861</v>
       </c>
       <c r="AF5" t="n">
-        <v>97.01764705882353</v>
+        <v>97.018</v>
       </c>
       <c r="AG5" t="n">
-        <v>96.36111111111111</v>
+        <v>96.361</v>
       </c>
       <c r="AH5" t="n">
         <v>96.97199999999999</v>
@@ -1031,25 +1031,25 @@
         <v>91.7</v>
       </c>
       <c r="C6" t="n">
-        <v>51.91428571428571</v>
+        <v>51.914</v>
       </c>
       <c r="D6" t="n">
-        <v>51.91176470588236</v>
+        <v>51.912</v>
       </c>
       <c r="E6" t="n">
-        <v>53.71111111111111</v>
+        <v>53.711</v>
       </c>
       <c r="F6" t="n">
-        <v>53.18888888888889</v>
+        <v>53.189</v>
       </c>
       <c r="G6" t="n">
-        <v>52.30625</v>
+        <v>52.306</v>
       </c>
       <c r="H6" t="n">
         <v>52.025</v>
       </c>
       <c r="I6" t="n">
-        <v>51.63333333333333</v>
+        <v>51.633</v>
       </c>
       <c r="J6" t="n">
         <v>51.375</v>
@@ -1058,49 +1058,49 @@
         <v>52.8</v>
       </c>
       <c r="L6" t="n">
-        <v>52.84999999999999</v>
+        <v>52.85</v>
       </c>
       <c r="M6" t="n">
-        <v>52.04705882352941</v>
+        <v>52.047</v>
       </c>
       <c r="N6" t="n">
         <v>51.7</v>
       </c>
       <c r="O6" t="n">
-        <v>51.64117647058823</v>
+        <v>51.641</v>
       </c>
       <c r="P6" t="n">
-        <v>51.51666666666667</v>
+        <v>51.517</v>
       </c>
       <c r="Q6" t="n">
-        <v>51.34375</v>
+        <v>51.344</v>
       </c>
       <c r="R6" t="n">
-        <v>51.22941176470588</v>
+        <v>51.229</v>
       </c>
       <c r="S6" t="n">
         <v>51.05</v>
       </c>
       <c r="T6" t="n">
-        <v>51.93333333333334</v>
+        <v>51.933</v>
       </c>
       <c r="U6" t="n">
-        <v>51.35555555555555</v>
+        <v>51.356</v>
       </c>
       <c r="V6" t="n">
-        <v>51.27058823529412</v>
+        <v>51.271</v>
       </c>
       <c r="W6" t="n">
-        <v>51.30555555555556</v>
+        <v>51.306</v>
       </c>
       <c r="X6" t="n">
-        <v>51.82941176470588</v>
+        <v>51.829</v>
       </c>
       <c r="Y6" t="n">
-        <v>51.24444444444444</v>
+        <v>51.244</v>
       </c>
       <c r="Z6" t="n">
-        <v>52.9375</v>
+        <v>52.938</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>51.04444444444445</v>
+        <v>51.044</v>
       </c>
       <c r="AE6" t="n">
-        <v>50.71111111111111</v>
+        <v>50.711</v>
       </c>
       <c r="AF6" t="n">
-        <v>50.56470588235294</v>
+        <v>50.565</v>
       </c>
       <c r="AG6" t="n">
-        <v>51.08888888888889</v>
+        <v>51.089</v>
       </c>
       <c r="AH6" t="n">
         <v>51.769</v>
@@ -1148,73 +1148,73 @@
         <v>92.09999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>87.31428571428572</v>
+        <v>87.31399999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>87.98823529411764</v>
+        <v>87.988</v>
       </c>
       <c r="E7" t="n">
-        <v>88.61111111111111</v>
+        <v>88.611</v>
       </c>
       <c r="F7" t="n">
-        <v>88.17777777777778</v>
+        <v>88.178</v>
       </c>
       <c r="G7" t="n">
-        <v>87.95625</v>
+        <v>87.956</v>
       </c>
       <c r="H7" t="n">
-        <v>87.73125</v>
+        <v>87.73099999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>87.53888888888889</v>
+        <v>87.539</v>
       </c>
       <c r="J7" t="n">
         <v>88.2</v>
       </c>
       <c r="K7" t="n">
-        <v>89.22777777777777</v>
+        <v>89.22799999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>89.12777777777778</v>
+        <v>89.128</v>
       </c>
       <c r="M7" t="n">
-        <v>89.14117647058823</v>
+        <v>89.14100000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>89.18125000000001</v>
+        <v>89.181</v>
       </c>
       <c r="O7" t="n">
-        <v>88.27058823529411</v>
+        <v>88.271</v>
       </c>
       <c r="P7" t="n">
-        <v>88.65555555555555</v>
+        <v>88.65600000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>88.20625</v>
+        <v>88.206</v>
       </c>
       <c r="R7" t="n">
-        <v>87.82352941176471</v>
+        <v>87.824</v>
       </c>
       <c r="S7" t="n">
         <v>88.15000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>88.47777777777777</v>
+        <v>88.47799999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>87.9388888888889</v>
+        <v>87.93899999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>87.94117647058823</v>
+        <v>87.941</v>
       </c>
       <c r="W7" t="n">
-        <v>88.12777777777778</v>
+        <v>88.128</v>
       </c>
       <c r="X7" t="n">
-        <v>88.28823529411765</v>
+        <v>88.288</v>
       </c>
       <c r="Y7" t="n">
-        <v>88.22777777777777</v>
+        <v>88.22799999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>87.55</v>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>88.03333333333333</v>
+        <v>88.033</v>
       </c>
       <c r="AE7" t="n">
-        <v>88.33888888888889</v>
+        <v>88.339</v>
       </c>
       <c r="AF7" t="n">
-        <v>88.10000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>87.69444444444444</v>
+        <v>87.694</v>
       </c>
       <c r="AH7" t="n">
         <v>88.215</v>
@@ -1268,73 +1268,73 @@
         <v>82</v>
       </c>
       <c r="D8" t="n">
-        <v>83.65882352941176</v>
+        <v>83.65900000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>82.88888888888889</v>
+        <v>82.889</v>
       </c>
       <c r="F8" t="n">
-        <v>79.54444444444444</v>
+        <v>79.544</v>
       </c>
       <c r="G8" t="n">
-        <v>78.99375000000001</v>
+        <v>78.994</v>
       </c>
       <c r="H8" t="n">
-        <v>78.14375</v>
+        <v>78.14400000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>77.02777777777777</v>
+        <v>77.02800000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>78.28749999999999</v>
+        <v>78.288</v>
       </c>
       <c r="K8" t="n">
-        <v>78.98333333333333</v>
+        <v>78.983</v>
       </c>
       <c r="L8" t="n">
-        <v>78.91111111111111</v>
+        <v>78.911</v>
       </c>
       <c r="M8" t="n">
-        <v>79.91176470588235</v>
+        <v>79.91200000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>79.66249999999999</v>
+        <v>79.66200000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>78.11176470588236</v>
+        <v>78.11199999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>78.30555555555556</v>
+        <v>78.306</v>
       </c>
       <c r="Q8" t="n">
-        <v>78.04375</v>
+        <v>78.044</v>
       </c>
       <c r="R8" t="n">
-        <v>77.9470588235294</v>
+        <v>77.947</v>
       </c>
       <c r="S8" t="n">
-        <v>79.05625000000001</v>
+        <v>79.056</v>
       </c>
       <c r="T8" t="n">
-        <v>79.84444444444445</v>
+        <v>79.84399999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>78.34444444444445</v>
+        <v>78.34399999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>79.0764705882353</v>
+        <v>79.07599999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>79.26666666666667</v>
+        <v>79.267</v>
       </c>
       <c r="X8" t="n">
-        <v>78.28823529411765</v>
+        <v>78.288</v>
       </c>
       <c r="Y8" t="n">
-        <v>78.42777777777778</v>
+        <v>78.428</v>
       </c>
       <c r="Z8" t="n">
-        <v>77.91249999999999</v>
+        <v>77.91200000000001</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1352,16 +1352,16 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>78.1888888888889</v>
+        <v>78.18899999999999</v>
       </c>
       <c r="AE8" t="n">
-        <v>78.00555555555555</v>
+        <v>78.006</v>
       </c>
       <c r="AF8" t="n">
-        <v>77.28823529411765</v>
+        <v>77.288</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.30555555555556</v>
+        <v>77.306</v>
       </c>
       <c r="AH8" t="n">
         <v>78.98</v>
@@ -1382,73 +1382,73 @@
         <v>93.3</v>
       </c>
       <c r="C9" t="n">
-        <v>87.49285714285715</v>
+        <v>87.49299999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>89.47647058823529</v>
+        <v>89.476</v>
       </c>
       <c r="E9" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>82.75555555555555</v>
+        <v>82.756</v>
       </c>
       <c r="G9" t="n">
-        <v>82.14375</v>
+        <v>82.14400000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>83.81874999999999</v>
+        <v>83.819</v>
       </c>
       <c r="I9" t="n">
         <v>82.84999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>82.91875</v>
+        <v>82.919</v>
       </c>
       <c r="K9" t="n">
-        <v>82.92222222222222</v>
+        <v>82.922</v>
       </c>
       <c r="L9" t="n">
-        <v>83.93333333333334</v>
+        <v>83.93300000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>81.26470588235294</v>
+        <v>81.265</v>
       </c>
       <c r="N9" t="n">
-        <v>79.93125000000001</v>
+        <v>79.931</v>
       </c>
       <c r="O9" t="n">
-        <v>77.94117647058823</v>
+        <v>77.941</v>
       </c>
       <c r="P9" t="n">
-        <v>77.82777777777778</v>
+        <v>77.828</v>
       </c>
       <c r="Q9" t="n">
         <v>77.65000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>76.87647058823529</v>
+        <v>76.876</v>
       </c>
       <c r="S9" t="n">
-        <v>79.18125000000001</v>
+        <v>79.181</v>
       </c>
       <c r="T9" t="n">
-        <v>81.58888888888889</v>
+        <v>81.589</v>
       </c>
       <c r="U9" t="n">
-        <v>77.74444444444445</v>
+        <v>77.744</v>
       </c>
       <c r="V9" t="n">
-        <v>78.67647058823529</v>
+        <v>78.676</v>
       </c>
       <c r="W9" t="n">
-        <v>77.11666666666666</v>
+        <v>77.117</v>
       </c>
       <c r="X9" t="n">
-        <v>78.58823529411765</v>
+        <v>78.58799999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>78.06666666666666</v>
+        <v>78.06699999999999</v>
       </c>
       <c r="Z9" t="n">
         <v>83.875</v>
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>84.55555555555556</v>
+        <v>84.556</v>
       </c>
       <c r="AE9" t="n">
-        <v>83.56666666666666</v>
+        <v>83.56699999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>83.15882352941176</v>
+        <v>83.15900000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>84.07777777777778</v>
+        <v>84.078</v>
       </c>
       <c r="AH9" t="n">
         <v>81.7</v>
@@ -1499,76 +1499,76 @@
         <v>94.09999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>63.40714285714286</v>
+        <v>63.407</v>
       </c>
       <c r="D10" t="n">
-        <v>60.12941176470589</v>
+        <v>60.129</v>
       </c>
       <c r="E10" t="n">
         <v>59.7</v>
       </c>
       <c r="F10" t="n">
-        <v>57.15555555555555</v>
+        <v>57.156</v>
       </c>
       <c r="G10" t="n">
-        <v>56.34375</v>
+        <v>56.344</v>
       </c>
       <c r="H10" t="n">
-        <v>57.06875</v>
+        <v>57.069</v>
       </c>
       <c r="I10" t="n">
-        <v>57.26666666666667</v>
+        <v>57.267</v>
       </c>
       <c r="J10" t="n">
         <v>56.95</v>
       </c>
       <c r="K10" t="n">
-        <v>55.98333333333333</v>
+        <v>55.983</v>
       </c>
       <c r="L10" t="n">
-        <v>54.59444444444445</v>
+        <v>54.594</v>
       </c>
       <c r="M10" t="n">
-        <v>58.17058823529412</v>
+        <v>58.171</v>
       </c>
       <c r="N10" t="n">
-        <v>57.61875</v>
+        <v>57.619</v>
       </c>
       <c r="O10" t="n">
-        <v>56.08235294117647</v>
+        <v>56.082</v>
       </c>
       <c r="P10" t="n">
-        <v>55.72222222222222</v>
+        <v>55.722</v>
       </c>
       <c r="Q10" t="n">
-        <v>54.91875</v>
+        <v>54.919</v>
       </c>
       <c r="R10" t="n">
-        <v>54.94117647058823</v>
+        <v>54.941</v>
       </c>
       <c r="S10" t="n">
-        <v>59.3125</v>
+        <v>59.312</v>
       </c>
       <c r="T10" t="n">
-        <v>57.59444444444445</v>
+        <v>57.594</v>
       </c>
       <c r="U10" t="n">
-        <v>56.85555555555555</v>
+        <v>56.856</v>
       </c>
       <c r="V10" t="n">
-        <v>57.49411764705882</v>
+        <v>57.494</v>
       </c>
       <c r="W10" t="n">
-        <v>55.42222222222222</v>
+        <v>55.422</v>
       </c>
       <c r="X10" t="n">
-        <v>56.76470588235294</v>
+        <v>56.765</v>
       </c>
       <c r="Y10" t="n">
-        <v>56.06111111111111</v>
+        <v>56.061</v>
       </c>
       <c r="Z10" t="n">
-        <v>53.7875</v>
+        <v>53.788</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1586,16 +1586,16 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>52.47777777777778</v>
+        <v>52.478</v>
       </c>
       <c r="AE10" t="n">
-        <v>54.37777777777777</v>
+        <v>54.378</v>
       </c>
       <c r="AF10" t="n">
-        <v>55.61764705882353</v>
+        <v>55.618</v>
       </c>
       <c r="AG10" t="n">
-        <v>55.95555555555556</v>
+        <v>55.956</v>
       </c>
       <c r="AH10" t="n">
         <v>56.706</v>
@@ -1616,73 +1616,73 @@
         <v>94.5</v>
       </c>
       <c r="C11" t="n">
-        <v>87.00714285714285</v>
+        <v>87.00700000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>87.54705882352941</v>
+        <v>87.547</v>
       </c>
       <c r="E11" t="n">
-        <v>87.75555555555555</v>
+        <v>87.756</v>
       </c>
       <c r="F11" t="n">
-        <v>87.16666666666667</v>
+        <v>87.167</v>
       </c>
       <c r="G11" t="n">
-        <v>87.50624999999999</v>
+        <v>87.506</v>
       </c>
       <c r="H11" t="n">
-        <v>87.16875</v>
+        <v>87.169</v>
       </c>
       <c r="I11" t="n">
-        <v>87.17777777777778</v>
+        <v>87.178</v>
       </c>
       <c r="J11" t="n">
-        <v>87.56874999999999</v>
+        <v>87.569</v>
       </c>
       <c r="K11" t="n">
-        <v>87.29444444444444</v>
+        <v>87.294</v>
       </c>
       <c r="L11" t="n">
-        <v>87.40555555555555</v>
+        <v>87.40600000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>87.76470588235294</v>
+        <v>87.765</v>
       </c>
       <c r="N11" t="n">
-        <v>87.13124999999999</v>
+        <v>87.131</v>
       </c>
       <c r="O11" t="n">
-        <v>87.52941176470588</v>
+        <v>87.529</v>
       </c>
       <c r="P11" t="n">
-        <v>87.48888888888888</v>
+        <v>87.489</v>
       </c>
       <c r="Q11" t="n">
         <v>87.55</v>
       </c>
       <c r="R11" t="n">
-        <v>87.03529411764706</v>
+        <v>87.035</v>
       </c>
       <c r="S11" t="n">
         <v>87.27500000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>87.65555555555555</v>
+        <v>87.65600000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>87.26111111111112</v>
+        <v>87.261</v>
       </c>
       <c r="V11" t="n">
-        <v>87.17058823529412</v>
+        <v>87.17100000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>88.12777777777778</v>
+        <v>88.128</v>
       </c>
       <c r="X11" t="n">
-        <v>86.90588235294118</v>
+        <v>86.90600000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>87.19444444444444</v>
+        <v>87.194</v>
       </c>
       <c r="Z11" t="n">
         <v>87.05</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>87.63333333333334</v>
+        <v>87.633</v>
       </c>
       <c r="AE11" t="n">
-        <v>87.10555555555555</v>
+        <v>87.10599999999999</v>
       </c>
       <c r="AF11" t="n">
-        <v>87.03529411764706</v>
+        <v>87.035</v>
       </c>
       <c r="AG11" t="n">
-        <v>87.13888888888889</v>
+        <v>87.139</v>
       </c>
       <c r="AH11" t="n">
         <v>87.345</v>
@@ -1733,76 +1733,76 @@
         <v>95.3</v>
       </c>
       <c r="C12" t="n">
-        <v>94.32142857142857</v>
+        <v>94.321</v>
       </c>
       <c r="D12" t="n">
-        <v>94.76470588235294</v>
+        <v>94.765</v>
       </c>
       <c r="E12" t="n">
-        <v>94.06666666666666</v>
+        <v>94.06699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.16666666666667</v>
+        <v>94.167</v>
       </c>
       <c r="G12" t="n">
-        <v>94.71875</v>
+        <v>94.71899999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>94.16249999999999</v>
+        <v>94.16200000000001</v>
       </c>
       <c r="I12" t="n">
         <v>94.15000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>94.30625000000001</v>
+        <v>94.306</v>
       </c>
       <c r="K12" t="n">
-        <v>94.03333333333333</v>
+        <v>94.033</v>
       </c>
       <c r="L12" t="n">
-        <v>93.80555555555556</v>
+        <v>93.806</v>
       </c>
       <c r="M12" t="n">
         <v>93.7</v>
       </c>
       <c r="N12" t="n">
-        <v>94.93125000000001</v>
+        <v>94.931</v>
       </c>
       <c r="O12" t="n">
-        <v>94.28235294117647</v>
+        <v>94.282</v>
       </c>
       <c r="P12" t="n">
-        <v>94.02222222222223</v>
+        <v>94.02200000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>94.45</v>
       </c>
       <c r="R12" t="n">
-        <v>93.68235294117646</v>
+        <v>93.682</v>
       </c>
       <c r="S12" t="n">
-        <v>94.21875</v>
+        <v>94.21899999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>94.32777777777778</v>
+        <v>94.328</v>
       </c>
       <c r="U12" t="n">
-        <v>94.87222222222222</v>
+        <v>94.872</v>
       </c>
       <c r="V12" t="n">
-        <v>94.42941176470588</v>
+        <v>94.429</v>
       </c>
       <c r="W12" t="n">
-        <v>94.40555555555555</v>
+        <v>94.40600000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>93.66470588235293</v>
+        <v>93.66500000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>94.47777777777777</v>
+        <v>94.47799999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>94.4375</v>
+        <v>94.438</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1820,16 +1820,16 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>94.85555555555555</v>
+        <v>94.85599999999999</v>
       </c>
       <c r="AE12" t="n">
-        <v>93.96111111111111</v>
+        <v>93.961</v>
       </c>
       <c r="AF12" t="n">
-        <v>93.87058823529412</v>
+        <v>93.871</v>
       </c>
       <c r="AG12" t="n">
-        <v>94.06666666666666</v>
+        <v>94.06699999999999</v>
       </c>
       <c r="AH12" t="n">
         <v>94.255</v>
@@ -1850,25 +1850,25 @@
         <v>95.7</v>
       </c>
       <c r="C13" t="n">
-        <v>79.19285714285715</v>
+        <v>79.193</v>
       </c>
       <c r="D13" t="n">
-        <v>78.01764705882353</v>
+        <v>78.018</v>
       </c>
       <c r="E13" t="n">
-        <v>76.98888888888888</v>
+        <v>76.989</v>
       </c>
       <c r="F13" t="n">
-        <v>78.1888888888889</v>
+        <v>78.18899999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>77.60625</v>
+        <v>77.60599999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>78.33750000000001</v>
+        <v>78.33799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>77.90555555555555</v>
+        <v>77.90600000000001</v>
       </c>
       <c r="J13" t="n">
         <v>77.875</v>
@@ -1877,49 +1877,49 @@
         <v>77.90000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>78.09444444444445</v>
+        <v>78.09399999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>76.56470588235294</v>
+        <v>76.565</v>
       </c>
       <c r="N13" t="n">
-        <v>78.29375</v>
+        <v>78.294</v>
       </c>
       <c r="O13" t="n">
-        <v>78.40588235294118</v>
+        <v>78.40600000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>76.46666666666667</v>
+        <v>76.467</v>
       </c>
       <c r="Q13" t="n">
-        <v>75.29375</v>
+        <v>75.294</v>
       </c>
       <c r="R13" t="n">
-        <v>76.73529411764706</v>
+        <v>76.735</v>
       </c>
       <c r="S13" t="n">
-        <v>77.22500000000001</v>
+        <v>77.22499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>78.42777777777778</v>
+        <v>78.428</v>
       </c>
       <c r="U13" t="n">
-        <v>78.76111111111112</v>
+        <v>78.761</v>
       </c>
       <c r="V13" t="n">
-        <v>78.72941176470589</v>
+        <v>78.729</v>
       </c>
       <c r="W13" t="n">
-        <v>77.31666666666666</v>
+        <v>77.31699999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>77.84705882352942</v>
+        <v>77.84699999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>76.90555555555555</v>
+        <v>76.90600000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>77.4875</v>
+        <v>77.488</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1937,16 +1937,16 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>76.87777777777778</v>
+        <v>76.878</v>
       </c>
       <c r="AE13" t="n">
-        <v>76.60555555555555</v>
+        <v>76.60599999999999</v>
       </c>
       <c r="AF13" t="n">
-        <v>77.10000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>76.22777777777777</v>
+        <v>76.22799999999999</v>
       </c>
       <c r="AH13" t="n">
         <v>77.54900000000001</v>
@@ -1967,70 +1967,70 @@
         <v>97.3</v>
       </c>
       <c r="C14" t="n">
-        <v>70.97142857142858</v>
+        <v>70.971</v>
       </c>
       <c r="D14" t="n">
-        <v>71.62941176470588</v>
+        <v>71.629</v>
       </c>
       <c r="E14" t="n">
-        <v>70.72222222222223</v>
+        <v>70.72199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>72.53333333333333</v>
+        <v>72.533</v>
       </c>
       <c r="G14" t="n">
-        <v>70.9375</v>
+        <v>70.938</v>
       </c>
       <c r="H14" t="n">
-        <v>71.58125</v>
+        <v>71.581</v>
       </c>
       <c r="I14" t="n">
-        <v>70.1888888888889</v>
+        <v>70.18899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>71.96250000000001</v>
+        <v>71.962</v>
       </c>
       <c r="K14" t="n">
-        <v>71.49444444444444</v>
+        <v>71.494</v>
       </c>
       <c r="L14" t="n">
-        <v>72.37222222222222</v>
+        <v>72.372</v>
       </c>
       <c r="M14" t="n">
-        <v>68.65294117647058</v>
+        <v>68.65300000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>69.2625</v>
+        <v>69.262</v>
       </c>
       <c r="O14" t="n">
-        <v>69.84117647058824</v>
+        <v>69.84099999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>70.48333333333333</v>
+        <v>70.483</v>
       </c>
       <c r="Q14" t="n">
         <v>69.34999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>69.12352941176471</v>
+        <v>69.124</v>
       </c>
       <c r="S14" t="n">
-        <v>68.91249999999999</v>
+        <v>68.91200000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>71.75555555555555</v>
+        <v>71.756</v>
       </c>
       <c r="U14" t="n">
-        <v>71.71666666666667</v>
+        <v>71.717</v>
       </c>
       <c r="V14" t="n">
-        <v>73.87058823529412</v>
+        <v>73.871</v>
       </c>
       <c r="W14" t="n">
-        <v>72.70555555555556</v>
+        <v>72.706</v>
       </c>
       <c r="X14" t="n">
-        <v>69.88823529411764</v>
+        <v>69.88800000000001</v>
       </c>
       <c r="Y14" t="n">
         <v>72.15000000000001</v>
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>75.15555555555555</v>
+        <v>75.15600000000001</v>
       </c>
       <c r="AE14" t="n">
-        <v>77.33333333333333</v>
+        <v>77.333</v>
       </c>
       <c r="AF14" t="n">
-        <v>76.21176470588235</v>
+        <v>76.212</v>
       </c>
       <c r="AG14" t="n">
-        <v>84.44999999999999</v>
+        <v>84.45</v>
       </c>
       <c r="AH14" t="n">
         <v>71.964</v>
@@ -2084,73 +2084,73 @@
         <v>98.09999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>82.15714285714286</v>
+        <v>82.157</v>
       </c>
       <c r="D15" t="n">
-        <v>82.04117647058824</v>
+        <v>82.041</v>
       </c>
       <c r="E15" t="n">
         <v>82</v>
       </c>
       <c r="F15" t="n">
-        <v>83.72222222222223</v>
+        <v>83.72199999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>81.55625000000001</v>
+        <v>81.556</v>
       </c>
       <c r="H15" t="n">
-        <v>82.06874999999999</v>
+        <v>82.069</v>
       </c>
       <c r="I15" t="n">
-        <v>81.31666666666666</v>
+        <v>81.31699999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>81.45625</v>
+        <v>81.456</v>
       </c>
       <c r="K15" t="n">
-        <v>82.40555555555555</v>
+        <v>82.40600000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>82.11111111111111</v>
+        <v>82.111</v>
       </c>
       <c r="M15" t="n">
-        <v>81.53529411764706</v>
+        <v>81.535</v>
       </c>
       <c r="N15" t="n">
         <v>81.65000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>81.02941176470588</v>
+        <v>81.029</v>
       </c>
       <c r="P15" t="n">
-        <v>79.18333333333334</v>
+        <v>79.18300000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>80.03125</v>
+        <v>80.03100000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>80.21176470588235</v>
+        <v>80.212</v>
       </c>
       <c r="S15" t="n">
-        <v>80.4375</v>
+        <v>80.438</v>
       </c>
       <c r="T15" t="n">
-        <v>82.08333333333333</v>
+        <v>82.083</v>
       </c>
       <c r="U15" t="n">
         <v>80.15000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>80.5529411764706</v>
+        <v>80.553</v>
       </c>
       <c r="W15" t="n">
-        <v>79.08333333333333</v>
+        <v>79.083</v>
       </c>
       <c r="X15" t="n">
-        <v>80.89999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>81.37222222222222</v>
+        <v>81.372</v>
       </c>
       <c r="Z15" t="n">
         <v>80.8</v>
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>80.96666666666667</v>
+        <v>80.967</v>
       </c>
       <c r="AE15" t="n">
-        <v>80.0611111111111</v>
+        <v>80.06100000000001</v>
       </c>
       <c r="AF15" t="n">
-        <v>80.62941176470588</v>
+        <v>80.629</v>
       </c>
       <c r="AG15" t="n">
-        <v>81.16111111111111</v>
+        <v>81.161</v>
       </c>
       <c r="AH15" t="n">
         <v>81.167</v>
@@ -2201,76 +2201,76 @@
         <v>98.5</v>
       </c>
       <c r="C16" t="n">
-        <v>46.87857142857143</v>
+        <v>46.879</v>
       </c>
       <c r="D16" t="n">
-        <v>46.80588235294118</v>
+        <v>46.806</v>
       </c>
       <c r="E16" t="n">
-        <v>45.96666666666667</v>
+        <v>45.967</v>
       </c>
       <c r="F16" t="n">
-        <v>47.77777777777778</v>
+        <v>47.778</v>
       </c>
       <c r="G16" t="n">
-        <v>48.08125</v>
+        <v>48.081</v>
       </c>
       <c r="H16" t="n">
         <v>47.05</v>
       </c>
       <c r="I16" t="n">
-        <v>46.67222222222222</v>
+        <v>46.672</v>
       </c>
       <c r="J16" t="n">
         <v>47.125</v>
       </c>
       <c r="K16" t="n">
-        <v>46.84444444444445</v>
+        <v>46.844</v>
       </c>
       <c r="L16" t="n">
-        <v>46.87777777777777</v>
+        <v>46.878</v>
       </c>
       <c r="M16" t="n">
-        <v>46.32941176470588</v>
+        <v>46.329</v>
       </c>
       <c r="N16" t="n">
-        <v>49.6625</v>
+        <v>49.662</v>
       </c>
       <c r="O16" t="n">
         <v>48.7</v>
       </c>
       <c r="P16" t="n">
-        <v>49.31111111111111</v>
+        <v>49.311</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.73125</v>
+        <v>47.731</v>
       </c>
       <c r="R16" t="n">
-        <v>49.22941176470588</v>
+        <v>49.229</v>
       </c>
       <c r="S16" t="n">
         <v>47.975</v>
       </c>
       <c r="T16" t="n">
-        <v>46.88333333333333</v>
+        <v>46.883</v>
       </c>
       <c r="U16" t="n">
-        <v>45.82222222222222</v>
+        <v>45.822</v>
       </c>
       <c r="V16" t="n">
-        <v>46.52352941176471</v>
+        <v>46.524</v>
       </c>
       <c r="W16" t="n">
-        <v>47.44444444444444</v>
+        <v>47.444</v>
       </c>
       <c r="X16" t="n">
-        <v>46.50588235294118</v>
+        <v>46.506</v>
       </c>
       <c r="Y16" t="n">
-        <v>46.15000000000001</v>
+        <v>46.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>45.6375</v>
+        <v>45.638</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>44.54444444444444</v>
+        <v>44.544</v>
       </c>
       <c r="AE16" t="n">
-        <v>46.62777777777777</v>
+        <v>46.628</v>
       </c>
       <c r="AF16" t="n">
-        <v>46.59411764705882</v>
+        <v>46.594</v>
       </c>
       <c r="AG16" t="n">
-        <v>47.17777777777778</v>
+        <v>47.178</v>
       </c>
       <c r="AH16" t="n">
         <v>47.105</v>
@@ -2318,76 +2318,76 @@
         <v>99.3</v>
       </c>
       <c r="C17" t="n">
-        <v>91.44285714285715</v>
+        <v>91.443</v>
       </c>
       <c r="D17" t="n">
-        <v>91.89999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>90.98888888888888</v>
+        <v>90.989</v>
       </c>
       <c r="F17" t="n">
-        <v>92.53333333333333</v>
+        <v>92.533</v>
       </c>
       <c r="G17" t="n">
-        <v>90.16875</v>
+        <v>90.169</v>
       </c>
       <c r="H17" t="n">
-        <v>92.01875</v>
+        <v>92.01900000000001</v>
       </c>
       <c r="I17" t="n">
         <v>89</v>
       </c>
       <c r="J17" t="n">
-        <v>89.86875000000001</v>
+        <v>89.869</v>
       </c>
       <c r="K17" t="n">
-        <v>91.92222222222222</v>
+        <v>91.922</v>
       </c>
       <c r="L17" t="n">
         <v>91.45</v>
       </c>
       <c r="M17" t="n">
-        <v>91.74117647058823</v>
+        <v>91.741</v>
       </c>
       <c r="N17" t="n">
-        <v>90.66875</v>
+        <v>90.669</v>
       </c>
       <c r="O17" t="n">
-        <v>82.07058823529412</v>
+        <v>82.071</v>
       </c>
       <c r="P17" t="n">
-        <v>89.35555555555555</v>
+        <v>89.35599999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>89.46875</v>
+        <v>89.46899999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>89.79411764705883</v>
+        <v>89.794</v>
       </c>
       <c r="S17" t="n">
-        <v>91.56874999999999</v>
+        <v>91.569</v>
       </c>
       <c r="T17" t="n">
-        <v>91.58888888888889</v>
+        <v>91.589</v>
       </c>
       <c r="U17" t="n">
-        <v>91.8111111111111</v>
+        <v>91.81100000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>90.04117647058824</v>
+        <v>90.041</v>
       </c>
       <c r="W17" t="n">
-        <v>87.87222222222222</v>
+        <v>87.872</v>
       </c>
       <c r="X17" t="n">
-        <v>91.38235294117646</v>
+        <v>91.38200000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>91.57222222222222</v>
+        <v>91.572</v>
       </c>
       <c r="Z17" t="n">
-        <v>91.66249999999999</v>
+        <v>91.66200000000001</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>89.04444444444444</v>
+        <v>89.044</v>
       </c>
       <c r="AE17" t="n">
-        <v>90.67777777777778</v>
+        <v>90.678</v>
       </c>
       <c r="AF17" t="n">
-        <v>89.97647058823529</v>
+        <v>89.976</v>
       </c>
       <c r="AG17" t="n">
-        <v>91.37222222222222</v>
+        <v>91.372</v>
       </c>
       <c r="AH17" t="n">
         <v>90.46299999999999</v>
@@ -2435,76 +2435,76 @@
         <v>99.7</v>
       </c>
       <c r="C18" t="n">
-        <v>88.66428571428571</v>
+        <v>88.664</v>
       </c>
       <c r="D18" t="n">
-        <v>89.04705882352941</v>
+        <v>89.047</v>
       </c>
       <c r="E18" t="n">
-        <v>88.14444444444445</v>
+        <v>88.14400000000001</v>
       </c>
       <c r="F18" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>88.63124999999999</v>
+        <v>88.631</v>
       </c>
       <c r="H18" t="n">
-        <v>89.49375000000001</v>
+        <v>89.494</v>
       </c>
       <c r="I18" t="n">
-        <v>88.68888888888888</v>
+        <v>88.68899999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>88.91875</v>
+        <v>88.919</v>
       </c>
       <c r="K18" t="n">
-        <v>90.21111111111111</v>
+        <v>90.211</v>
       </c>
       <c r="L18" t="n">
-        <v>89.76111111111112</v>
+        <v>89.761</v>
       </c>
       <c r="M18" t="n">
-        <v>89.08235294117648</v>
+        <v>89.08199999999999</v>
       </c>
       <c r="N18" t="n">
         <v>89.7</v>
       </c>
       <c r="O18" t="n">
-        <v>89.32352941176471</v>
+        <v>89.324</v>
       </c>
       <c r="P18" t="n">
-        <v>88.95555555555556</v>
+        <v>88.956</v>
       </c>
       <c r="Q18" t="n">
-        <v>89.71250000000001</v>
+        <v>89.712</v>
       </c>
       <c r="R18" t="n">
-        <v>89.21764705882353</v>
+        <v>89.218</v>
       </c>
       <c r="S18" t="n">
-        <v>89.31874999999999</v>
+        <v>89.319</v>
       </c>
       <c r="T18" t="n">
-        <v>90.02222222222223</v>
+        <v>90.02200000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>90.05555555555556</v>
+        <v>90.056</v>
       </c>
       <c r="V18" t="n">
-        <v>89.87647058823529</v>
+        <v>89.876</v>
       </c>
       <c r="W18" t="n">
-        <v>89.8111111111111</v>
+        <v>89.81100000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>89.82352941176471</v>
+        <v>89.824</v>
       </c>
       <c r="Y18" t="n">
-        <v>89.8111111111111</v>
+        <v>89.81100000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>89.5625</v>
+        <v>89.562</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2522,16 +2522,16 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>90.25555555555555</v>
+        <v>90.256</v>
       </c>
       <c r="AE18" t="n">
-        <v>89.19444444444444</v>
+        <v>89.194</v>
       </c>
       <c r="AF18" t="n">
-        <v>89.25882352941177</v>
+        <v>89.259</v>
       </c>
       <c r="AG18" t="n">
-        <v>89.40555555555555</v>
+        <v>89.40600000000001</v>
       </c>
       <c r="AH18" t="n">
         <v>89.44799999999999</v>
@@ -2552,76 +2552,76 @@
         <v>101.7</v>
       </c>
       <c r="C19" t="n">
-        <v>95.07142857142857</v>
+        <v>95.071</v>
       </c>
       <c r="D19" t="n">
-        <v>95.45294117647059</v>
+        <v>95.453</v>
       </c>
       <c r="E19" t="n">
-        <v>95.16666666666667</v>
+        <v>95.167</v>
       </c>
       <c r="F19" t="n">
-        <v>96.01111111111112</v>
+        <v>96.011</v>
       </c>
       <c r="G19" t="n">
-        <v>95.2375</v>
+        <v>95.238</v>
       </c>
       <c r="H19" t="n">
-        <v>95.89375</v>
+        <v>95.89400000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>95.45555555555556</v>
+        <v>95.456</v>
       </c>
       <c r="J19" t="n">
-        <v>95.34375</v>
+        <v>95.34399999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>95.74444444444445</v>
+        <v>95.744</v>
       </c>
       <c r="L19" t="n">
-        <v>95.15555555555555</v>
+        <v>95.15600000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>93.96470588235294</v>
+        <v>93.965</v>
       </c>
       <c r="N19" t="n">
-        <v>94.33125</v>
+        <v>94.331</v>
       </c>
       <c r="O19" t="n">
-        <v>94.28235294117647</v>
+        <v>94.282</v>
       </c>
       <c r="P19" t="n">
-        <v>93.86111111111111</v>
+        <v>93.861</v>
       </c>
       <c r="Q19" t="n">
-        <v>93.70625</v>
+        <v>93.706</v>
       </c>
       <c r="R19" t="n">
-        <v>93.65882352941176</v>
+        <v>93.65900000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>93.48125</v>
+        <v>93.48099999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>92.98888888888888</v>
+        <v>92.989</v>
       </c>
       <c r="U19" t="n">
-        <v>93.1888888888889</v>
+        <v>93.18899999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>93.32352941176471</v>
+        <v>93.324</v>
       </c>
       <c r="W19" t="n">
-        <v>93.22222222222223</v>
+        <v>93.22199999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>92.97647058823529</v>
+        <v>92.976</v>
       </c>
       <c r="Y19" t="n">
-        <v>93.07777777777778</v>
+        <v>93.078</v>
       </c>
       <c r="Z19" t="n">
-        <v>92.96250000000001</v>
+        <v>92.962</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>88.22222222222223</v>
+        <v>88.22199999999999</v>
       </c>
       <c r="AE19" t="n">
-        <v>94.92777777777778</v>
+        <v>94.928</v>
       </c>
       <c r="AF19" t="n">
-        <v>95.78235294117647</v>
+        <v>95.782</v>
       </c>
       <c r="AG19" t="n">
-        <v>95.53333333333333</v>
+        <v>95.533</v>
       </c>
       <c r="AH19" t="n">
         <v>94.215</v>
@@ -2669,76 +2669,76 @@
         <v>105.7</v>
       </c>
       <c r="C20" t="n">
-        <v>44.26428571428572</v>
+        <v>44.264</v>
       </c>
       <c r="D20" t="n">
         <v>43.4</v>
       </c>
       <c r="E20" t="n">
-        <v>42.86666666666667</v>
+        <v>42.867</v>
       </c>
       <c r="F20" t="n">
-        <v>43.77777777777778</v>
+        <v>43.778</v>
       </c>
       <c r="G20" t="n">
-        <v>45.04375</v>
+        <v>45.044</v>
       </c>
       <c r="H20" t="n">
-        <v>43.9125</v>
+        <v>43.912</v>
       </c>
       <c r="I20" t="n">
-        <v>44.13888888888889</v>
+        <v>44.139</v>
       </c>
       <c r="J20" t="n">
-        <v>42.84375</v>
+        <v>42.844</v>
       </c>
       <c r="K20" t="n">
-        <v>44.13888888888889</v>
+        <v>44.139</v>
       </c>
       <c r="L20" t="n">
         <v>43.75</v>
       </c>
       <c r="M20" t="n">
-        <v>48.47647058823529</v>
+        <v>48.476</v>
       </c>
       <c r="N20" t="n">
-        <v>47.18125</v>
+        <v>47.181</v>
       </c>
       <c r="O20" t="n">
-        <v>44.35294117647059</v>
+        <v>44.353</v>
       </c>
       <c r="P20" t="n">
-        <v>45.83888888888889</v>
+        <v>45.839</v>
       </c>
       <c r="Q20" t="n">
-        <v>46.7625</v>
+        <v>46.762</v>
       </c>
       <c r="R20" t="n">
-        <v>47.58235294117647</v>
+        <v>47.582</v>
       </c>
       <c r="S20" t="n">
-        <v>45.7375</v>
+        <v>45.738</v>
       </c>
       <c r="T20" t="n">
-        <v>42.88888888888889</v>
+        <v>42.889</v>
       </c>
       <c r="U20" t="n">
-        <v>41.15000000000001</v>
+        <v>41.15</v>
       </c>
       <c r="V20" t="n">
-        <v>42.50588235294118</v>
+        <v>42.506</v>
       </c>
       <c r="W20" t="n">
-        <v>43.88333333333333</v>
+        <v>43.883</v>
       </c>
       <c r="X20" t="n">
-        <v>43.54705882352941</v>
+        <v>43.547</v>
       </c>
       <c r="Y20" t="n">
-        <v>42.27777777777778</v>
+        <v>42.278</v>
       </c>
       <c r="Z20" t="n">
-        <v>44.6375</v>
+        <v>44.638</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2756,16 +2756,16 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>41.86666666666667</v>
+        <v>41.867</v>
       </c>
       <c r="AE20" t="n">
-        <v>42.42222222222222</v>
+        <v>42.422</v>
       </c>
       <c r="AF20" t="n">
-        <v>41.86470588235294</v>
+        <v>41.865</v>
       </c>
       <c r="AG20" t="n">
-        <v>43.45555555555556</v>
+        <v>43.456</v>
       </c>
       <c r="AH20" t="n">
         <v>44.092</v>
@@ -2786,73 +2786,73 @@
         <v>106.1</v>
       </c>
       <c r="C21" t="n">
-        <v>93.22857142857143</v>
+        <v>93.229</v>
       </c>
       <c r="D21" t="n">
-        <v>93.49411764705881</v>
+        <v>93.494</v>
       </c>
       <c r="E21" t="n">
-        <v>93.6888888888889</v>
+        <v>93.68899999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>93.8111111111111</v>
+        <v>93.81100000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>93.94374999999999</v>
+        <v>93.944</v>
       </c>
       <c r="H21" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>93.85555555555555</v>
+        <v>93.85599999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>93.83125</v>
+        <v>93.831</v>
       </c>
       <c r="K21" t="n">
-        <v>93.98888888888888</v>
+        <v>93.989</v>
       </c>
       <c r="L21" t="n">
-        <v>93.70555555555556</v>
+        <v>93.706</v>
       </c>
       <c r="M21" t="n">
-        <v>93.75882352941177</v>
+        <v>93.759</v>
       </c>
       <c r="N21" t="n">
         <v>93.425</v>
       </c>
       <c r="O21" t="n">
-        <v>93.77058823529411</v>
+        <v>93.771</v>
       </c>
       <c r="P21" t="n">
-        <v>94.01111111111112</v>
+        <v>94.011</v>
       </c>
       <c r="Q21" t="n">
         <v>93.72499999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>93.47647058823529</v>
+        <v>93.476</v>
       </c>
       <c r="S21" t="n">
         <v>93.77500000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>93.89444444444445</v>
+        <v>93.89400000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>94.01111111111112</v>
+        <v>94.011</v>
       </c>
       <c r="V21" t="n">
-        <v>93.82352941176471</v>
+        <v>93.824</v>
       </c>
       <c r="W21" t="n">
-        <v>94.14444444444445</v>
+        <v>94.14400000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>93.49411764705883</v>
+        <v>93.494</v>
       </c>
       <c r="Y21" t="n">
-        <v>93.55555555555556</v>
+        <v>93.556</v>
       </c>
       <c r="Z21" t="n">
         <v>93.34999999999999</v>
@@ -2873,16 +2873,16 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>93.14444444444445</v>
+        <v>93.14400000000001</v>
       </c>
       <c r="AE21" t="n">
-        <v>93.41111111111111</v>
+        <v>93.411</v>
       </c>
       <c r="AF21" t="n">
-        <v>93.57058823529412</v>
+        <v>93.571</v>
       </c>
       <c r="AG21" t="n">
-        <v>93.66111111111111</v>
+        <v>93.661</v>
       </c>
       <c r="AH21" t="n">
         <v>93.71299999999999</v>
@@ -2903,76 +2903,76 @@
         <v>106.9</v>
       </c>
       <c r="C22" t="n">
-        <v>95.87142857142858</v>
+        <v>95.871</v>
       </c>
       <c r="D22" t="n">
         <v>92.8</v>
       </c>
       <c r="E22" t="n">
-        <v>89.73333333333333</v>
+        <v>89.733</v>
       </c>
       <c r="F22" t="n">
-        <v>95.21111111111111</v>
+        <v>95.211</v>
       </c>
       <c r="G22" t="n">
-        <v>91.8875</v>
+        <v>91.88800000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>91.70625</v>
+        <v>91.706</v>
       </c>
       <c r="I22" t="n">
-        <v>92.10555555555555</v>
+        <v>92.10599999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>91.3625</v>
+        <v>91.36199999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>91.63333333333334</v>
+        <v>91.633</v>
       </c>
       <c r="L22" t="n">
-        <v>91.57222222222222</v>
+        <v>91.572</v>
       </c>
       <c r="M22" t="n">
-        <v>91.5529411764706</v>
+        <v>91.553</v>
       </c>
       <c r="N22" t="n">
-        <v>92.46875</v>
+        <v>92.46899999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>92.87058823529412</v>
+        <v>92.871</v>
       </c>
       <c r="P22" t="n">
-        <v>92.88888888888889</v>
+        <v>92.889</v>
       </c>
       <c r="Q22" t="n">
         <v>92.97499999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>92.32352941176471</v>
+        <v>92.324</v>
       </c>
       <c r="S22" t="n">
-        <v>92.9375</v>
+        <v>92.938</v>
       </c>
       <c r="T22" t="n">
-        <v>95.68333333333334</v>
+        <v>95.68300000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>92.74444444444445</v>
+        <v>92.744</v>
       </c>
       <c r="V22" t="n">
-        <v>92.45882352941176</v>
+        <v>92.459</v>
       </c>
       <c r="W22" t="n">
         <v>92.95</v>
       </c>
       <c r="X22" t="n">
-        <v>92.75882352941177</v>
+        <v>92.759</v>
       </c>
       <c r="Y22" t="n">
-        <v>92.52777777777777</v>
+        <v>92.52800000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>95.41249999999999</v>
+        <v>95.41200000000001</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>95.22222222222223</v>
+        <v>95.22199999999999</v>
       </c>
       <c r="AE22" t="n">
-        <v>92.56666666666666</v>
+        <v>92.56699999999999</v>
       </c>
       <c r="AF22" t="n">
-        <v>92.39411764705882</v>
+        <v>92.39400000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>92.54444444444444</v>
+        <v>92.544</v>
       </c>
       <c r="AH22" t="n">
         <v>92.827</v>
@@ -3020,70 +3020,70 @@
         <v>107.3</v>
       </c>
       <c r="C23" t="n">
-        <v>89.27142857142857</v>
+        <v>89.271</v>
       </c>
       <c r="D23" t="n">
         <v>88.7</v>
       </c>
       <c r="E23" t="n">
-        <v>88.43333333333334</v>
+        <v>88.43300000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>88.98888888888888</v>
+        <v>88.989</v>
       </c>
       <c r="G23" t="n">
-        <v>88.9875</v>
+        <v>88.988</v>
       </c>
       <c r="H23" t="n">
         <v>89.02500000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>68.03333333333333</v>
+        <v>68.033</v>
       </c>
       <c r="J23" t="n">
-        <v>46.18125</v>
+        <v>46.181</v>
       </c>
       <c r="K23" t="n">
-        <v>88.91111111111111</v>
+        <v>88.911</v>
       </c>
       <c r="L23" t="n">
-        <v>88.96666666666667</v>
+        <v>88.967</v>
       </c>
       <c r="M23" t="n">
-        <v>88.75294117647059</v>
+        <v>88.753</v>
       </c>
       <c r="N23" t="n">
         <v>88.875</v>
       </c>
       <c r="O23" t="n">
-        <v>89.19411764705882</v>
+        <v>89.194</v>
       </c>
       <c r="P23" t="n">
-        <v>89.50555555555555</v>
+        <v>89.506</v>
       </c>
       <c r="Q23" t="n">
-        <v>89.79375</v>
+        <v>89.794</v>
       </c>
       <c r="R23" t="n">
-        <v>89.64117647058823</v>
+        <v>89.64100000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>89.63124999999999</v>
+        <v>89.631</v>
       </c>
       <c r="T23" t="n">
-        <v>89.18333333333334</v>
+        <v>89.18300000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>89.21111111111111</v>
+        <v>89.211</v>
       </c>
       <c r="V23" t="n">
-        <v>89.43529411764706</v>
+        <v>89.435</v>
       </c>
       <c r="W23" t="n">
-        <v>90.08333333333333</v>
+        <v>90.083</v>
       </c>
       <c r="X23" t="n">
-        <v>89.84705882352942</v>
+        <v>89.84699999999999</v>
       </c>
       <c r="Y23" t="n">
         <v>89.40000000000001</v>
@@ -3107,16 +3107,16 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>89.64444444444445</v>
+        <v>89.64400000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>89.58333333333333</v>
+        <v>89.583</v>
       </c>
       <c r="AF23" t="n">
-        <v>90.15882352941176</v>
+        <v>90.15900000000001</v>
       </c>
       <c r="AG23" t="n">
-        <v>89.69999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="AH23" t="n">
         <v>87.014</v>
@@ -3140,73 +3140,73 @@
         <v>92.8</v>
       </c>
       <c r="D24" t="n">
-        <v>91.98823529411764</v>
+        <v>91.988</v>
       </c>
       <c r="E24" t="n">
-        <v>91.35555555555555</v>
+        <v>91.35599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>91.8111111111111</v>
+        <v>91.81100000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>92.20625</v>
+        <v>92.206</v>
       </c>
       <c r="H24" t="n">
         <v>92.84999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>92.96666666666667</v>
+        <v>92.967</v>
       </c>
       <c r="J24" t="n">
-        <v>92.0625</v>
+        <v>92.062</v>
       </c>
       <c r="K24" t="n">
-        <v>92.05000000000001</v>
+        <v>92.05</v>
       </c>
       <c r="L24" t="n">
-        <v>91.97222222222223</v>
+        <v>91.97199999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>91.98235294117647</v>
+        <v>91.982</v>
       </c>
       <c r="N24" t="n">
-        <v>91.9875</v>
+        <v>91.988</v>
       </c>
       <c r="O24" t="n">
-        <v>91.82352941176471</v>
+        <v>91.824</v>
       </c>
       <c r="P24" t="n">
-        <v>92.13888888888889</v>
+        <v>92.139</v>
       </c>
       <c r="Q24" t="n">
         <v>92.77500000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>92.60000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>92.78125</v>
+        <v>92.78100000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>92.92222222222222</v>
+        <v>92.922</v>
       </c>
       <c r="U24" t="n">
-        <v>91.83888888888889</v>
+        <v>91.839</v>
       </c>
       <c r="V24" t="n">
-        <v>92.83529411764707</v>
+        <v>92.83499999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>92.70555555555556</v>
+        <v>92.706</v>
       </c>
       <c r="X24" t="n">
-        <v>92.88823529411764</v>
+        <v>92.88800000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>92.35555555555555</v>
+        <v>92.35599999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>93.1125</v>
+        <v>93.11199999999999</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3224,16 +3224,16 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>93.01111111111112</v>
+        <v>93.011</v>
       </c>
       <c r="AE24" t="n">
-        <v>92.70555555555556</v>
+        <v>92.706</v>
       </c>
       <c r="AF24" t="n">
-        <v>92.98235294117647</v>
+        <v>92.982</v>
       </c>
       <c r="AG24" t="n">
-        <v>93.02222222222223</v>
+        <v>93.02200000000001</v>
       </c>
       <c r="AH24" t="n">
         <v>92.44799999999999</v>
